--- a/products/store_b/out/07_Bill_Tracker_Payment_Calendar.xlsx
+++ b/products/store_b/out/07_Bill_Tracker_Payment_Calendar.xlsx
@@ -972,11 +972,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="68622118"/>
-        <c:axId val="43484982"/>
+        <c:axId val="273348"/>
+        <c:axId val="52769528"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="68622118"/>
+        <c:axId val="273348"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1008,7 +1008,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43484982"/>
+        <c:crossAx val="52769528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1016,7 +1016,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43484982"/>
+        <c:axId val="52769528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1058,7 +1058,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68622118"/>
+        <c:crossAx val="273348"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
